--- a/samples/outputs/XQ-4157308_parsed.xlsx
+++ b/samples/outputs/XQ-4157308_parsed.xlsx
@@ -115,6 +115,12 @@
   </x:si>
   <x:si>
     <x:t>USD</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Term-Months</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Term in months</x:t>
   </x:si>
   <x:si>
     <x:t>*</x:t>
@@ -483,7 +489,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:AA4"/>
+  <x:dimension ref="A1:AA5"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:sheetData>
     <x:row r="1" spans="1:27">
@@ -613,11 +619,46 @@
       </x:c>
     </x:row>
     <x:row r="4" spans="1:27">
+      <x:c r="A4" s="0">
+        <x:v>2</x:v>
+      </x:c>
       <x:c r="B4" s="0" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="D4" s="0" t="s">
         <x:v>33</x:v>
       </x:c>
-      <x:c r="D4" s="0" t="s">
+      <x:c r="E4" s="0" t="s">
         <x:v>34</x:v>
+      </x:c>
+      <x:c r="F4" s="0">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="K4" s="0">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="R4" s="0" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="S4" s="0" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="T4" s="0">
+        <x:v>1E-06</x:v>
+      </x:c>
+      <x:c r="U4" s="0">
+        <x:v>1E-06</x:v>
+      </x:c>
+      <x:c r="V4" s="0">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="5" spans="1:27">
+      <x:c r="B5" s="0" t="s">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="D5" s="0" t="s">
+        <x:v>36</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/samples/outputs/XQ-4157308_parsed.xlsx
+++ b/samples/outputs/XQ-4157308_parsed.xlsx
@@ -644,10 +644,10 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="T4" s="0">
-        <x:v>1E-06</x:v>
+        <x:v>0.0001</x:v>
       </x:c>
       <x:c r="U4" s="0">
-        <x:v>1E-06</x:v>
+        <x:v>0.0001</x:v>
       </x:c>
       <x:c r="V4" s="0">
         <x:v>1</x:v>
